--- a/benchmark/generated_files/CRED-2_V_036.xlsx
+++ b/benchmark/generated_files/CRED-2_V_036.xlsx
@@ -446,28 +446,28 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Banca: CartaSì/Nexi</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Tipo conto: Carta di credito</t>
+          <t>Filiale: SEDE CENTRALE</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Numero carta: **** **** **** 7890</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Numero carta: **** **** **** 7890</t>
+          <t>Tipo conto: Carta di credito</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Intestatario: Laura Bianchi</t>
+          <t>Codice cliente: 216613</t>
         </is>
       </c>
     </row>
@@ -500,18 +500,18 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>46027</v>
+        <v>46024</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>46028</v>
+        <v>46024</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 136,38 EUR DEL 05.01.2026 A (ITA) PANIFICIO TOSI</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 7784 CONAD CITY CORSICO</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>136.38</v>
+        <v>138.11</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
@@ -521,18 +521,18 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>46027</v>
+        <v>46025</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>46028</v>
+        <v>46025</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 92,16 EUR DEL 05.01.2026 A (ITA) CONAD CITY ROMA</t>
+          <t>Disposizione - RIF:210792982 BEN. TINTORIA RAPIDA CENTRO</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>92.16</v>
+        <v>80.25</v>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
@@ -542,18 +542,18 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>46027</v>
+        <v>46025</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>46027</v>
+        <v>46025</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 14,13 EUR DEL 05.01.2026 A (ITA) PESCHERIA DEL PORTO</t>
+          <t>Pagam. POS - PAGAMENTO POS 146,97 EUR DEL 03.01.2026 A (ITA) DECATHLON ASSAGO</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>14.13</v>
+        <v>146.97</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
@@ -563,18 +563,18 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>46029</v>
+        <v>46028</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>46029</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 25,02 EUR DEL 07.01.2026 A (ITA) COOP LOMBARDIA</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 1053 CHURCH'S</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>25.02</v>
+        <v>125.93</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
@@ -587,15 +587,15 @@
         <v>46029</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>46031</v>
+        <v>46029</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - WIND TRE S.P.A. MOBILE</t>
+          <t>Pagam. POS - PAGAMENTO POS 169,13 EUR DEL 07.01.2026 A (ITA) SALMOIRAGHI &amp; VIGANÒ</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>5.92</v>
+        <v>169.13</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
@@ -605,18 +605,18 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>46031</v>
+        <v>46030</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>46033</v>
+        <v>46030</v>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 43,92 EUR DEL 09.01.2026 A (ITA) H&amp;M HENNES AND MAURITZ</t>
+          <t>Pagam. POS - PAGAMENTO POS 25,72 EUR DEL 08.01.2026 A (ITA) UDON VERONA</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>43.92</v>
+        <v>25.72</v>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
@@ -626,18 +626,18 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>46032</v>
+        <v>46030</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>46032</v>
+        <v>46031</v>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 126,04 EUR DEL 10.01.2026 A (ITA) PESCHERIA DEL PORTO</t>
+          <t>Pagam. POS - PAGAMENTO POS 90,03 EUR DEL 08.01.2026 A (ITA) HISTOIRE D'OR</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>126.04</v>
+        <v>90.03</v>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
@@ -647,18 +647,18 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>46033</v>
+        <v>46030</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>46033</v>
+        <v>46030</v>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Disposizione - RIF:210354144 BEN. AFFITTO APPARTAMENTO SOFIA BOLOGNA</t>
+          <t>Disposizione - RIF:214531535 BEN. UNIVERSITA' DEGLI STUDI DI BOLOGNA</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>355.7</v>
+        <v>674.97</v>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
@@ -668,18 +668,18 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>46034</v>
+        <v>46032</v>
       </c>
       <c r="B15" s="2" t="n">
         <v>46034</v>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 229,21 EUR DEL 12.01.2026 A (ITA) FARMACIA COMUNALE</t>
+          <t>Pagam. POS - PAGAMENTO POS 147,21 EUR DEL 10.01.2026 A (ITA) EKOM CAGLIARI</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>229.21</v>
+        <v>147.21</v>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
@@ -689,18 +689,18 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>46034</v>
+        <v>46032</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>46034</v>
+        <v>46032</v>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 191,37 EUR DEL 12.01.2026 A (ITA) FARMACIA DR ROSSI</t>
+          <t>Pagam. POS - PAGAMENTO POS 58,95 EUR DEL 10.01.2026 A (ITA) EXKI</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>191.37</v>
+        <v>58.95</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
@@ -710,18 +710,18 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>46036</v>
+        <v>46034</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>46036</v>
+        <v>46034</v>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 53,78 EUR DEL 14.01.2026 A (ITA) MCDONALD'S ITALIA</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 8189 O'TACOS</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>53.78</v>
+        <v>78.79000000000001</v>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
@@ -731,18 +731,18 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>46038</v>
+        <v>46035</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>46038</v>
+        <v>46035</v>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 78,34 EUR DEL 16.01.2026 A (ITA) CALZEDONIA GROUP</t>
+          <t>Pagam. POS - PAGAMENTO POS 70,55 EUR DEL 13.01.2026 A (ITA) GABOR GENOVA</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>78.34</v>
+        <v>70.55</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
@@ -752,18 +752,18 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>46038</v>
+        <v>46039</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>46038</v>
+        <v>46039</v>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - JUST EAT ITALY SRL</t>
+          <t>Pagam. POS - PAGAMENTO POS 71,22 EUR DEL 17.01.2026 A (ITA) CALZEDONIA GROUP</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>54.36</v>
+        <v>71.22</v>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
@@ -773,18 +773,18 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>46038</v>
+        <v>46040</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>46039</v>
+        <v>46040</v>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 51,19 EUR DEL 16.01.2026 A (ITA) LIDL ITALIA SRL</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 3198 AUTOGRILL BOLOGNA</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>51.19</v>
+        <v>35.19</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
@@ -794,18 +794,18 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>46043</v>
+        <v>46041</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>46043</v>
+        <v>46041</v>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - GENERALI ITALIA POLIZZA VITA</t>
+          <t>Pagam. POS - PAGAMENTO POS 132,40 EUR DEL 19.01.2026 A (ITA) PRIMADONNA</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>78.27</v>
+        <v>132.4</v>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
@@ -815,18 +815,18 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>46044</v>
+        <v>46042</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>46045</v>
+        <v>46043</v>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 596,20 EUR DEL 22.01.2026 A (ITA) CARTOLIBRERIA IL PAPIRO</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 4634 NAU!</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>596.2</v>
+        <v>156.99</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
@@ -836,18 +836,18 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>46044</v>
+        <v>46042</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>46046</v>
+        <v>46042</v>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>PAGAMENTO CONTACTLESS CARTA **** 3886 OVS S.P.A.</t>
+          <t>Pagam. POS - PAGAMENTO POS 162,99 EUR DEL 20.01.2026 A (ITA) PESCHERIA DEL PORTO</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>102.93</v>
+        <v>162.99</v>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
@@ -857,18 +857,18 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>46044</v>
+        <v>46046</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>46044</v>
+        <v>46046</v>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Disposizione - RIF:214385930 BEN. UNIVERSITA' DEGLI STUDI DI BOLOGNA</t>
+          <t>Pagam. POS - PAGAMENTO POS 167,46 EUR DEL 24.01.2026 A (ITA) MINI MIX</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>767.46</v>
+        <v>167.46</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
@@ -885,11 +885,11 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - NETFLIX INTERNATIONAL B.V.</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 7368 L'ISOLA DEI TESORI</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>7.69</v>
+        <v>45.73</v>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
@@ -899,18 +899,18 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 37,53 EUR DEL 25.01.2026 A (ITA) OTTICA AVANZI</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 1890 TRATTORIA LA PERGOLA</t>
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>37.53</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
@@ -920,18 +920,18 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>46047</v>
+        <v>46049</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>46047</v>
+        <v>46050</v>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 69,37 EUR DEL 25.01.2026 A (ITA) MACELLERIA BONI</t>
+          <t>Pagam. POS - PAGAMENTO POS 12,68 EUR DEL 27.01.2026 A (ITA) BREWDOG</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>69.37</v>
+        <v>12.68</v>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
@@ -941,18 +941,18 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>46049</v>
+        <v>46052</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>46049</v>
+        <v>46052</v>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 59,19 EUR DEL 27.01.2026 A (ITA) CENTRO DIAGNOSTICO SAN DONATO</t>
+          <t>Pagam. POS - PAGAMENTO POS 81,18 EUR DEL 30.01.2026 A (ITA) EMISFERO NAPOLI</t>
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>59.19</v>
+        <v>81.18000000000001</v>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
@@ -962,18 +962,18 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>46050</v>
+        <v>46052</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>46050</v>
+        <v>46052</v>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 37,38 EUR DEL 28.01.2026 A (ITA) ZARA ITALIA SRL</t>
+          <t>Pagam. POS - PAGAMENTO POS 21,87 EUR DEL 30.01.2026 A (ITA) PANIFICIO TOSI</t>
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>37.38</v>
+        <v>21.87</v>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
@@ -986,15 +986,15 @@
         <v>46052</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>46053</v>
+        <v>46052</v>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - MENSA SCOLASTICA COMUNE DI MILANO</t>
+          <t>Addebito SDD - GOOGLE *CLOUD STORAGE</t>
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>308.02</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
@@ -1004,18 +1004,18 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>46054</v>
+        <v>46053</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>46055</v>
+        <v>46053</v>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - TELECOM ITALIA S.P.A. FIBRA</t>
+          <t>Pagam. POS - PAGAMENTO POS 75,19 EUR DEL 31.01.2026 A (ITA) MCDONALD'S ITALIA</t>
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>71.25</v>
+        <v>75.19</v>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
@@ -1025,18 +1025,18 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>46055</v>
+        <v>46054</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>46057</v>
+        <v>46054</v>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>PAGAMENTO CONTACTLESS CARTA **** 4816 CONAD SUPERSTORE</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 3412 PENNY</t>
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>17.43</v>
+        <v>41.29</v>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
@@ -1046,18 +1046,18 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>46056</v>
+        <v>46054</v>
       </c>
       <c r="B33" s="2" t="n">
         <v>46056</v>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 23,17 EUR DEL 03.02.2026 A (ITA) DECATHLON ASSAGO</t>
+          <t>Pagam. POS - PAGAMENTO POS 21,80 EUR DEL 01.02.2026 A (ITA) DECATHLON ASSAGO</t>
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>23.17</v>
+        <v>21.8</v>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
@@ -1067,18 +1067,18 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>46056</v>
+        <v>46055</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>46056</v>
+        <v>46055</v>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 153,90 EUR DEL 03.02.2026 A (ITA) MACELLERIA BONI</t>
+          <t>Pagam. POS - PAGAMENTO POS 31,04 EUR DEL 02.02.2026 A (ITA) ALICE MODENA</t>
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>153.9</v>
+        <v>31.04</v>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
@@ -1091,15 +1091,15 @@
         <v>46056</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 56,72 EUR DEL 03.02.2026 A (ITA) TABACCHERIA N.12</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 5451 CHURCH'S</t>
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>56.72</v>
+        <v>148.12</v>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
@@ -1112,15 +1112,15 @@
         <v>46057</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>46059</v>
+        <v>46057</v>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>PAGAMENTO CONTACTLESS CARTA **** 5597 ESSELUNGA S.P.A.</t>
+          <t>Pagam. POS - PAGAMENTO POS 95,37 EUR DEL 04.02.2026 A (ITA) IN'S MERCATO PERUGIA</t>
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>173.93</v>
+        <v>95.37</v>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
@@ -1130,18 +1130,18 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>46062</v>
+        <v>46057</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>46063</v>
+        <v>46057</v>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - SPOTIFY AB</t>
+          <t>Pagam. POS - PAGAMENTO POS 95,30 EUR DEL 04.02.2026 A (ITA) NAU!</t>
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>6.4</v>
+        <v>95.3</v>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
@@ -1151,18 +1151,18 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>46063</v>
+        <v>46057</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>46063</v>
+        <v>46059</v>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 15,56 EUR DEL 10.02.2026 A (ITA) ZARA ITALIA SRL</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 9260 ARCAPLANET ROZZANO</t>
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>15.56</v>
+        <v>95.01000000000001</v>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
@@ -1172,18 +1172,18 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>46064</v>
+        <v>46058</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>46065</v>
+        <v>46058</v>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 197,44 EUR DEL 11.02.2026 A (ITA) FARMACIA COMUNALE</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 6664 PENNY</t>
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>197.44</v>
+        <v>18.71</v>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
@@ -1193,18 +1193,18 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>46065</v>
+        <v>46060</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>46065</v>
+        <v>46062</v>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 411,89 EUR DEL 12.02.2026 A (ITA) CARTOLIBRERIA IL PAPIRO</t>
+          <t>AMAZON.IT MARKETPLACE - ORDINE 402-216400075</t>
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>411.89</v>
+        <v>8.19</v>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
@@ -1214,18 +1214,18 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>46065</v>
+        <v>46061</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>46065</v>
+        <v>46062</v>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 85,19 EUR DEL 12.02.2026 A (ITA) ESSELUNGA MILANO</t>
+          <t>Addebito SDD - GOOGLE *CLOUD STORAGE</t>
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>85.19</v>
+        <v>11.95</v>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
@@ -1235,18 +1235,18 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>46066</v>
+        <v>46062</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>46066</v>
+        <v>46064</v>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - JUST EAT ITALY SRL</t>
+          <t>Pagam. POS - PAGAMENTO POS 9,84 EUR DEL 09.02.2026 A (ITA) MEDIAWORLD CARUGATE</t>
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>52.15</v>
+        <v>9.84</v>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
@@ -1256,18 +1256,18 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>46066</v>
+        <v>46062</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>46066</v>
+        <v>46062</v>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>PAGAMENTO CONTACTLESS CARTA **** 4066 TRATTORIA LA PERGOLA</t>
+          <t>Pagam. POS - PAGAMENTO POS 600,75 EUR DEL 09.02.2026 A (ITA) LIBRACCIO</t>
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>48.28</v>
+        <v>600.75</v>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
@@ -1277,18 +1277,18 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>46067</v>
+        <v>46063</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>46067</v>
+        <v>46065</v>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 44,63 EUR DEL 14.02.2026 A (ITA) PIZZERIA NAPOLI</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 4946 LIBRACCIO LIVORNO</t>
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>44.63</v>
+        <v>18.51</v>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
@@ -1298,18 +1298,18 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>46069</v>
+        <v>46063</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>46069</v>
+        <v>46063</v>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>PAGAMENTO CONTACTLESS CARTA **** 7245 ESSELUNGA S.P.A.</t>
+          <t>Pagam. POS - PAGAMENTO POS 12,87 EUR DEL 10.02.2026 A (ITA) TACO BELL BOLOGNA</t>
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>20.82</v>
+        <v>12.87</v>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
@@ -1319,18 +1319,18 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>46069</v>
+        <v>46065</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>46069</v>
+        <v>46067</v>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 56,21 EUR DEL 16.02.2026 A (ITA) CALZEDONIA GROUP</t>
+          <t>Pagam. POS - PAGAMENTO POS 179,28 EUR DEL 12.02.2026 A (ITA) MERCATO RIONALE PORTA PALAZZO</t>
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>56.21</v>
+        <v>179.28</v>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
@@ -1340,18 +1340,18 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>46070</v>
+        <v>46066</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>46070</v>
+        <v>46067</v>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Disposizione - RIF:212637826 BEN. TINTORIA RAPIDA CENTRO</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 8623 SIGMA</t>
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>47.92</v>
+        <v>140.5</v>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
@@ -1361,18 +1361,18 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>46071</v>
+        <v>46066</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>46073</v>
+        <v>46066</v>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>PAGAMENTO CONTACTLESS CARTA **** 3551 CONAD SUPERSTORE</t>
+          <t>Pagam. POS - PAGAMENTO POS 29,30 EUR DEL 13.02.2026 A (ITA) THE COFFEE MESTRE</t>
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>46.31</v>
+        <v>29.3</v>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
@@ -1382,18 +1382,18 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>46071</v>
+        <v>46067</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>46073</v>
+        <v>46067</v>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 88,25 EUR DEL 18.02.2026 A (ITA) LIDL ITALIA SRL</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 5345 TRATTORIA LA PERGOLA</t>
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>88.25</v>
+        <v>55</v>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
@@ -1403,18 +1403,18 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>46071</v>
+        <v>46067</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>46071</v>
+        <v>46067</v>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - TELECOM ITALIA S.P.A. FIBRA</t>
+          <t>Addebito SDD - GOOGLE *CLOUD STORAGE</t>
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>77.52</v>
+        <v>10.17</v>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
@@ -1424,18 +1424,18 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>46072</v>
+        <v>46069</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>46074</v>
+        <v>46071</v>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - NETFLIX INTERNATIONAL B.V.</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 5016 ARD DISCOUNT ROMA</t>
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>7.14</v>
+        <v>130.76</v>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
@@ -1445,18 +1445,18 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>46073</v>
+        <v>46070</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>46075</v>
+        <v>46070</v>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 62,12 EUR DEL 20.02.2026 A (ITA) ROSTICCERIA DA MARIO</t>
+          <t>Pagam. POS - PAGAMENTO POS 158,82 EUR DEL 17.02.2026 A (ITA) MIX MARKT FIRENZE</t>
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>62.12</v>
+        <v>158.82</v>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
@@ -1466,18 +1466,18 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>46074</v>
+        <v>46073</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>46076</v>
+        <v>46073</v>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - DELIVEROO ITALY SRL</t>
+          <t>Pagam. POS - PAGAMENTO POS 15,72 EUR DEL 20.02.2026 A (ITA) TIGOTÀ</t>
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>57.18</v>
+        <v>15.72</v>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
@@ -1494,11 +1494,11 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 231,17 EUR DEL 22.02.2026 A (ITA) FARMACIA DR ROSSI</t>
+          <t>Addebito SDD - NETFLIX INTERNATIONAL B.V.</t>
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>231.17</v>
+        <v>7.42</v>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
@@ -1508,18 +1508,18 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 91,79 EUR DEL 23.02.2026 A (ITA) OTTICA AVANZI</t>
+          <t>Pagam. POS - PAGAMENTO POS 137,08 EUR DEL 24.02.2026 A (ITA) FARMACIA DR ROSSI</t>
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>91.79000000000001</v>
+        <v>137.08</v>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
@@ -1532,15 +1532,15 @@
         <v>46077</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>46079</v>
+        <v>46077</v>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 53,01 EUR DEL 24.02.2026 A (ITA) MERCATO RIONALE PORTA PALAZZO</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 9880 COOP</t>
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>53.01</v>
+        <v>15.42</v>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
@@ -1550,18 +1550,18 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B57" s="2" t="n">
         <v>46079</v>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 156,13 EUR DEL 25.02.2026 A (ITA) MERCATO RIONALE PORTA PALAZZO</t>
+          <t>Pagam. POS - PAGAMENTO POS 200,65 EUR DEL 26.02.2026 A (ITA) CENTRO DIAGNOSTICO SAN DONATO</t>
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>156.13</v>
+        <v>200.65</v>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
@@ -1571,18 +1571,18 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>46078</v>
+        <v>46080</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>46078</v>
+        <v>46080</v>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - JUST EAT ITALY SRL</t>
+          <t>Pagam. POS - PAGAMENTO POS 66,14 EUR DEL 27.02.2026 A (ITA) CADDY'S MARGHERA</t>
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>69.7</v>
+        <v>66.14</v>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
@@ -1592,18 +1592,18 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>46078</v>
+        <v>46080</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>PAGAMENTO CONTACTLESS CARTA **** 7359 CONAD SUPERSTORE</t>
+          <t>Addebito SDD - APPLE.COM/BILL</t>
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>165.53</v>
+        <v>11.48</v>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
@@ -1613,18 +1613,18 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>46080</v>
+        <v>46081</v>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 222,17 EUR DEL 26.02.2026 A (ITA) FARMACIA COMUNALE</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 8587 BUCHHANDLUNG WALTHER KÖNIG</t>
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>222.17</v>
+        <v>30.4</v>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
@@ -1634,18 +1634,18 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>46080</v>
+        <v>46081</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>46080</v>
+        <v>46081</v>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 44,27 EUR DEL 27.02.2026 A (ITA) RISTORANTE DA GINO</t>
+          <t>Pagam. POS - PAGAMENTO POS 35,46 EUR DEL 28.02.2026 A (ITA) IPER</t>
         </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>44.27</v>
+        <v>35.46</v>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Saldo finale: 17.954,62 EUR</t>
+          <t>Saldo finale: 24.312,40 EUR</t>
         </is>
       </c>
     </row>
